--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:16:59+00:00</t>
+    <t>2026-06-05T12:18:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:18:27+00:00</t>
+    <t>2026-06-05T12:21:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:21:59+00:00</t>
+    <t>2026-06-05T13:35:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T13:35:06+00:00</t>
+    <t>2026-08-04T12:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Practitioner|4.0.1</t>
+    <t>http://hl7.eu/fhir/base/StructureDefinition/practitioner-eu-core|2.0.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}name-or-identifier:identifier or name SHALL be present {identifier.exists() or name.exists()}</t>
   </si>
   <si>
     <t>PRD (as one example)</t>
@@ -673,7 +673,7 @@
 </t>
   </si>
   <si>
-    <t>An identifier for the person as this agent</t>
+    <t>Practitioner identifier</t>
   </si>
   <si>
     <t>An identifier that applies to this person in this role.</t>
@@ -1004,7 +1004,7 @@
 </t>
   </si>
   <si>
-    <t>The name(s) associated with the practitioner</t>
+    <t>Practitioner Name</t>
   </si>
   <si>
     <t>The name(s) associated with the practitioner.</t>
@@ -1247,7 +1247,7 @@
 </t>
   </si>
   <si>
-    <t>A contact detail for the practitioner (that apply to all roles)</t>
+    <t>Contact details for the practitioner</t>
   </si>
   <si>
     <t>A contact detail for the practitioner, e.g. a telephone number or an email address.</t>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>80</v>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:27:17+00:00</t>
+    <t>2026-08-04T15:42:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T15:42:07+00:00</t>
+    <t>2026-08-07T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T07:47:42+00:00</t>
+    <t>2026-08-07T08:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:01:10+00:00</t>
+    <t>2026-08-07T08:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:58:25+00:00</t>
+    <t>2026-08-07T11:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T11:55:57+00:00</t>
+    <t>2026-08-10T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T12:42:53+00:00</t>
+    <t>2026-08-10T13:14:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:14:57+00:00</t>
+    <t>2026-08-10T13:29:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:29:34+00:00</t>
+    <t>2026-08-10T13:33:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:33:35+00:00</t>
+    <t>2026-08-10T13:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:39:12+00:00</t>
+    <t>2026-08-10T13:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:42:57+00:00</t>
+    <t>2026-08-10T13:45:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:45:29+00:00</t>
+    <t>2026-08-10T13:54:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:54:17+00:00</t>
+    <t>2026-08-10T14:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T14:12:55+00:00</t>
+    <t>2026-08-10T14:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T14:29:18+00:00</t>
+    <t>2026-08-10T16:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:19:09+00:00</t>
+    <t>2026-08-10T16:22:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:22:30+00:00</t>
+    <t>2026-08-10T16:46:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:46:59+00:00</t>
+    <t>2026-08-11T07:24:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T07:24:13+00:00</t>
+    <t>2026-08-11T10:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T10:04:20+00:00</t>
+    <t>2026-08-11T11:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T11:39:02+00:00</t>
+    <t>2026-08-12T13:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T13:53:29+00:00</t>
+    <t>2026-08-12T14:08:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
